--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1117 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/23</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -998,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1056,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1167,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1228,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1278,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1339,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1389,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1450,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1500,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1561,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1611,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1672,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1722,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1783,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1833,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1894,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1944,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2005,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2055,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2116,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2166,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2227,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2277,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2338,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2388,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2449,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2499,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2560,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2610,562 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/23</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -751,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -784,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -808,17 +804,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -828,13 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3165,7 +3165,451 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -753,24 +753,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -862,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,17 +923,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -939,13 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -973,12 +981,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1006,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1014,10 +1022,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1045,7 +1069,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1084,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1117,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1141,33 +1169,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1228,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1252,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1417,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1450,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1474,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1600,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1672,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2227,7 +2275,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2338,7 +2386,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2449,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2560,7 +2608,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2671,7 +2719,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2782,7 +2830,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2893,7 +2941,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3004,7 +3052,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3072,7 +3120,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3115,7 +3163,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3129,7 +3177,7 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3226,7 +3274,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3284,22 +3332,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3337,7 +3385,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3351,7 +3399,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3376,7 +3424,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3395,22 +3443,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3448,7 +3496,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3487,7 +3535,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3506,22 +3554,22 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3559,7 +3607,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3573,7 +3621,7 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3603,11 +3651,697 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>1/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr"/>
-      <c r="AC28" s="2" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>—/25</t>
         </is>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1467,24 +1467,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1687,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,33 +1748,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1942,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1981,7 +1989,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2053,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2092,7 +2100,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2164,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2203,7 +2211,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2242,32 +2250,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -2275,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2299,33 +2311,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2425,7 +2441,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2497,7 +2513,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2536,7 +2552,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2608,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2735,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2957,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,7 +3068,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,7 +3179,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3274,7 +3290,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3385,7 +3401,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3496,7 +3512,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3607,7 +3623,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3722,7 +3738,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3776,7 +3792,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3853,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3948,7 +3964,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4002,7 +4018,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4079,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4117,7 +4133,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -4125,22 +4141,22 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4178,7 +4194,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4222,17 +4238,13 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4252,7 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4250,7 +4262,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4288,12 +4300,12 @@
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4307,41 +4319,1052 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr"/>
-      <c r="AC34" s="2" t="inlineStr">
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>7/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
         <is>
           <t>—/25</t>
         </is>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1193,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>11/25</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2061,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2172,7 +2176,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2287,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2341,7 +2345,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>8/25</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2406,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2513,7 +2517,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2591,32 +2595,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2624,7 +2632,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2648,33 +2656,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -2702,32 +2714,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2735,7 +2751,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2759,33 +2775,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -2813,32 +2833,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>176分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2846,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2870,17 +2894,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2890,13 +2914,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>15/25</t>
         </is>
       </c>
     </row>
@@ -2924,32 +2952,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2957,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2981,17 +3013,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3001,13 +3033,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -3035,32 +3071,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3068,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3092,33 +3132,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -3146,32 +3190,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3179,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3203,33 +3251,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -3257,32 +3309,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3290,7 +3346,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3314,33 +3370,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3461,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3479,32 +3539,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3512,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3536,17 +3600,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3556,13 +3620,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3662,7 +3730,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3738,7 +3806,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3777,7 +3845,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3792,7 +3860,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3888,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq59，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3853,7 +3921,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3861,10 +3929,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
           <t>09:26</t>
@@ -3931,32 +4015,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3964,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3988,17 +4076,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4008,12 +4096,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4079,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4133,7 +4221,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4233,7 +4321,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4305,7 +4393,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4359,7 +4447,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>11/25</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4508,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4531,7 +4619,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4585,7 +4673,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4734,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4757,7 +4845,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4868,7 +4956,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4979,7 +5067,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5037,22 +5125,22 @@
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5085,12 +5173,12 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5104,7 +5192,7 @@
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5134,13 +5222,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>8/25</t>
         </is>
       </c>
     </row>
@@ -5148,22 +5240,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5196,12 +5288,12 @@
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5245,17 +5337,13 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5404,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5370,6 +5458,922 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>13/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>6/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>9/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>7/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>10/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>1/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,13 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,13 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,18 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,13 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,13 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2220,13 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2330,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2345,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/25</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2456,7 +2480,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2567,7 +2591,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2686,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2805,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/25</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3162,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3281,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3400,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3535,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3654,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3745,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3860,7 +3884,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3917,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq59，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq63，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3921,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3987,7 +4011,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4025,24 +4049,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4052,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4101,12 +4125,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4134,32 +4158,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4167,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4191,17 +4219,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4211,17 +4239,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4249,32 +4277,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4282,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4306,17 +4338,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4326,13 +4358,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4360,32 +4396,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4393,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4417,37 +4457,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4475,32 +4515,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4508,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4532,17 +4576,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4552,13 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4586,32 +4634,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4619,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4643,17 +4695,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4663,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4701,32 +4753,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -4734,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4758,17 +4814,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4778,13 +4834,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4812,32 +4872,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -4845,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4869,33 +4933,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4923,32 +4991,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4956,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4980,17 +5052,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5000,13 +5072,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5034,32 +5110,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5067,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5091,17 +5171,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5111,13 +5191,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5217,7 +5301,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5232,7 +5316,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/25</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5343,7 +5427,7 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5454,7 +5538,7 @@
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5569,7 +5653,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5714,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5684,7 +5768,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5829,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5799,7 +5883,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5944,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5914,7 +5998,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5975,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6029,7 +6113,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6174,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6144,7 +6228,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6289,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6259,7 +6343,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6404,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6364,13 +6448,695 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr"/>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>—/25</t>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5001,24 +5001,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5120,24 +5120,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7140,6 +7140,121 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,13 +2474,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,13 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,22 +2703,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,17 +2827,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3298,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3305,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3424,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,7 +3647,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3654,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3884,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4487,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4733,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4963,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5186,7 +5194,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5201,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5229,32 +5237,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5262,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5286,17 +5298,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5306,17 +5318,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5344,32 +5356,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5377,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5401,17 +5417,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5421,13 +5437,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5455,32 +5475,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5488,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5512,17 +5536,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5532,13 +5556,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5566,32 +5594,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5599,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5623,37 +5655,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5681,32 +5713,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5714,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5738,17 +5774,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5758,17 +5794,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5796,32 +5832,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5829,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5853,17 +5893,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5873,17 +5913,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5983,7 +6023,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -5998,7 +6038,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6113,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6228,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6383,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6458,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6573,7 +6613,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,7 +6896,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6910,7 +6950,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6971,7 +7011,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7082,7 +7122,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7126,17 +7166,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7144,22 +7184,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7192,12 +7232,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7211,47 +7251,507 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>13/28</t>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,14 +1307,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,22 +3877,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,14 +4242,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,22 +4361,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,14 +4718,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5984,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6008,17 +6012,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6028,17 +6032,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6066,32 +6070,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6099,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,17 +6131,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6143,17 +6151,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6181,32 +6189,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6214,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6238,37 +6250,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6411,32 +6423,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6444,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6468,37 +6484,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6526,32 +6542,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6559,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6583,17 +6603,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6603,17 +6623,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6661,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq52，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6674,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6682,10 +6702,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
-      <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -6752,32 +6788,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6785,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6809,33 +6849,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6950,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7176,7 +7220,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7281,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7291,7 +7335,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7406,7 +7450,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7521,7 +7565,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7626,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7626,17 +7670,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7751,7 +7795,582 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,14 +2941,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>176.0</t>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5199,17 +5199,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5318,17 +5318,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5794,17 +5794,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6552,19 +6552,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq52，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq58，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6810,12 +6810,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6907,32 +6907,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -6940,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,17 +6968,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6984,17 +6988,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7026,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7055,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7079,17 +7087,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7099,13 +7107,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7145,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -7166,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7190,17 +7206,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7210,17 +7226,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7248,32 +7264,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7281,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7305,17 +7325,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7325,17 +7345,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7363,32 +7383,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7396,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7420,17 +7444,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7440,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7565,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7680,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7795,7 +7819,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7910,7 +7934,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7995,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8025,7 +8049,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8140,7 +8164,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8225,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8255,7 +8279,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8340,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8370,7 +8394,574 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,14 +1188,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2708,17 +2708,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>139.0</t>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,14 +3417,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,17 +3882,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,14 +4123,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5675,17 +5675,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5908,14 +5908,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>139.0</t>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6146,14 +6146,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6270,17 +6270,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7274,24 +7274,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,32 +7502,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,17 +7563,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7579,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7704,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7732,32 +7736,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7765,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7789,17 +7797,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7809,17 +7817,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7847,32 +7855,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7880,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7904,17 +7916,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7924,17 +7936,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7962,32 +7974,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7995,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8019,17 +8035,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8039,17 +8055,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8225,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8340,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8455,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8566,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8620,7 +8636,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8697,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8792,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8854,22 +8870,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8902,12 +8918,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8946,22 +8962,1053 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
+      <c r="AC73" s="2" t="inlineStr">
         <is>
           <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC81"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,22 +4242,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7746,24 +7746,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7984,24 +7984,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,22 +8050,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8093,32 +8093,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8126,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8150,17 +8154,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8170,17 +8174,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8208,32 +8212,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -8241,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8265,17 +8273,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8285,17 +8293,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8395,7 +8403,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8438,12 +8446,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -8471,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8479,10 +8487,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="2" t="inlineStr"/>
-      <c r="S68" s="2" t="inlineStr"/>
-      <c r="T68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8549,32 +8573,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8582,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8606,17 +8634,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8626,17 +8654,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8923,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9038,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9092,7 +9120,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9264,7 +9292,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9379,7 +9407,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9494,7 +9522,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9609,7 +9637,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9663,7 +9691,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9752,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9839,7 +9867,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9954,7 +9982,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10008,7 +10036,582 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5789,14 +5789,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5913,17 +5913,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7107,17 +7107,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,14 +7459,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8331,32 +8331,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8364,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8388,17 +8392,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8408,17 +8412,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8455,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq57，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -8479,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8573,36 +8577,32 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8634,17 +8634,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8654,17 +8654,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8803,32 +8803,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8836,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8860,32 +8864,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8918,32 +8922,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8951,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8975,17 +8983,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -8995,17 +9003,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9181,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9220,7 +9228,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9259,32 +9267,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9292,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9316,17 +9328,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9336,17 +9348,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9419,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9461,7 +9473,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9576,7 +9588,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9691,7 +9703,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9764,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9867,7 +9879,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9982,7 +9994,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10097,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10151,7 +10163,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10224,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10327,7 +10339,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10381,7 +10393,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10454,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10496,7 +10508,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10569,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10601,17 +10613,703 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB86" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr">
-        <is>
-          <t>2/29</t>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,13 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3723,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4084,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4441,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4679,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4733,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5036,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5155,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5274,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5393,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5750,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5869,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5908,17 +5912,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6341,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6579,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6633,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7063,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7102,7 +7106,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7182,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7301,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7420,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7773,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8011,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8249,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8303,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8840,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8894,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8944,12 +8948,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8959,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8998,7 +9002,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9074,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9156,32 +9160,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9189,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9213,17 +9221,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9233,13 +9241,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9277,12 +9289,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -9304,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9343,17 +9355,17 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9419,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9534,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9649,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9764,7 +9776,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9879,7 +9891,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9994,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10048,7 +10060,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10121,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10224,7 +10236,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10339,7 +10351,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10454,7 +10466,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10569,7 +10581,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10684,7 +10696,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10799,7 +10811,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10914,7 +10926,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11029,7 +11041,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11083,7 +11095,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11156,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11198,7 +11210,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11206,22 +11218,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11254,12 +11266,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11273,43 +11285,277 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W92" s="2" t="inlineStr">
+      <c r="W93" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X92" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y92" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z92" s="2" t="inlineStr">
+      <c r="Z93" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA92" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB92" s="2" t="inlineStr"/>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>—/29</t>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,22 +1188,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,14 +2703,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4127,22 +4127,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4489,17 +4489,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4603,22 +4603,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5084,17 +5084,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,14 +5674,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,22 +6150,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6389,17 +6389,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6627,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7582,14 +7582,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -9170,24 +9170,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9289,24 +9289,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9398,32 +9398,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9431,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9455,37 +9459,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9513,32 +9517,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9546,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9570,37 +9578,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9628,32 +9636,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9661,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9685,17 +9697,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9705,17 +9717,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9743,32 +9755,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9776,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9800,37 +9816,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9874,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9891,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9915,17 +9935,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9935,17 +9955,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9973,32 +9993,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10006,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10030,17 +10054,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10050,17 +10074,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10175,7 +10199,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10260,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10290,7 +10314,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10405,7 +10429,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10490,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10520,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10581,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10635,7 +10659,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10811,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10865,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10950,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10980,7 +11004,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11065,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11156,7 +11180,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11210,7 +11234,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11295,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11320,7 +11344,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11386,7 +11410,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11435,12 +11459,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -11448,22 +11472,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11496,12 +11520,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11515,47 +11539,737 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
         <is>
           <t>142.5</t>
         </is>
       </c>
-      <c r="AC94" s="2" t="inlineStr">
+      <c r="AC95" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6992,17 +6992,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,17 +7230,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10003,24 +10003,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10112,32 +10112,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10145,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10169,17 +10173,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10189,17 +10193,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10227,32 +10231,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -10260,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10284,17 +10292,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10304,17 +10312,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10342,32 +10350,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10375,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10399,17 +10411,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10419,17 +10431,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10457,32 +10469,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10490,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10514,17 +10530,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10534,17 +10550,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10720,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10759,7 +10775,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10802,32 +10818,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10835,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10859,17 +10879,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10879,7 +10899,7 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
@@ -10889,7 +10909,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11004,7 +11024,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11180,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11295,7 +11315,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11410,7 +11430,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11525,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11640,7 +11660,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11755,7 +11775,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11809,7 +11829,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11890,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11985,7 +12005,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12039,7 +12059,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12120,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12215,7 +12235,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12269,7 +12289,237 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东35路.xlsx
+++ b/data/export/2026-10-19-浦东35路.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,17 +2474,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4727,17 +4727,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,17 +7349,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,17 +9122,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,17 +9241,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10828,24 +10828,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10937,32 +10937,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10970,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10994,17 +10998,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11014,17 +11018,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11052,32 +11056,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11085,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11109,17 +11117,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11129,12 +11137,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11167,32 +11175,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11200,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11224,17 +11236,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11244,17 +11256,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11282,12 +11294,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -11315,7 +11327,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11323,10 +11335,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
-      <c r="S92" s="2" t="inlineStr"/>
-      <c r="T92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±2分钟；反向位置物理seq28（站名待映射） ETA 21分钟参与校验</t>
+        </is>
+      </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11369,7 +11397,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -11397,32 +11425,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11430,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11454,17 +11486,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11474,17 +11506,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11599,7 +11631,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11714,7 +11746,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11742,12 +11774,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11775,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11783,10 +11815,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -11829,7 +11877,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11938,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11944,7 +11992,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -11972,32 +12020,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -12005,7 +12057,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12029,17 +12081,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12049,17 +12101,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12120,7 +12172,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12174,7 +12226,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12289,7 +12341,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12402,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12404,7 +12456,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12517,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
